--- a/data/trans_orig/P16A09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259558</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269403</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240303</t>
+          <t>239517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254636</t>
+          <t>254594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>504644</t>
+          <t>502832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>521111</t>
+          <t>520994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46473</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481105</t>
+          <t>481740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491126</t>
+          <t>491040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463789</t>
+          <t>463787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484219</t>
+          <t>484387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950551</t>
+          <t>950296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972849</t>
+          <t>973404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19919</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309234</t>
+          <t>308241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317888</t>
+          <t>317853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320500</t>
+          <t>320938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331654</t>
+          <t>332230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634339</t>
+          <t>634612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647933</t>
+          <t>648429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343736</t>
+          <t>345027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355795</t>
+          <t>355745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347221</t>
+          <t>346909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362222</t>
+          <t>362308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697155</t>
+          <t>696715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715807</t>
+          <t>715485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>31703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43384</t>
+          <t>42914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186897</t>
+          <t>186103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199486</t>
+          <t>199226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175371</t>
+          <t>175965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194820</t>
+          <t>194187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367592</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391133</t>
+          <t>391153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259237</t>
+          <t>259461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268090</t>
+          <t>268827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260105</t>
+          <t>259915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273177</t>
+          <t>273061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523289</t>
+          <t>523940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538881</t>
+          <t>539352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>37853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>578632</t>
+          <t>577710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597995</t>
+          <t>598646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602922</t>
+          <t>602791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>621828</t>
+          <t>622182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1188279</t>
+          <t>1188063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1215537</t>
+          <t>1215393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>39348</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67022</t>
+          <t>69180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>66258</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102650</t>
+          <t>102548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699847</t>
+          <t>699195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720535</t>
+          <t>720319</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>716489</t>
+          <t>714331</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744011</t>
+          <t>744163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1423638</t>
+          <t>1423740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1458730</t>
+          <t>1460030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>115878</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>146473</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>199364</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>235279</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>298426</t>
+          <t>301417</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3159647</t>
+          <t>3160761</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3198449</t>
+          <t>3197225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3179833</t>
+          <t>3180742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3231347</t>
+          <t>3232724</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6356296</t>
+          <t>6353305</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6419443</t>
+          <t>6418544</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276088</t>
+          <t>276760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288210</t>
+          <t>288213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261356</t>
+          <t>261254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275139</t>
+          <t>275165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543573</t>
+          <t>543084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561411</t>
+          <t>561627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476826</t>
+          <t>478801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498139</t>
+          <t>498093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482682</t>
+          <t>485411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503684</t>
+          <t>504674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>971586</t>
+          <t>972073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>999688</t>
+          <t>999110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32143</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312739</t>
+          <t>312014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321108</t>
+          <t>321125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308877</t>
+          <t>310615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327443</t>
+          <t>329587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627827</t>
+          <t>627354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647598</t>
+          <t>647843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>352773</t>
+          <t>353258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367567</t>
+          <t>367364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347641</t>
+          <t>346614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367777</t>
+          <t>366968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706443</t>
+          <t>705563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730846</t>
+          <t>732152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>43337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196578</t>
+          <t>196829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209240</t>
+          <t>209174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188161</t>
+          <t>187051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206430</t>
+          <t>205593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390916</t>
+          <t>388872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>412027</t>
+          <t>411283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261362</t>
+          <t>261275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271836</t>
+          <t>270958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252934</t>
+          <t>253249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269928</t>
+          <t>268999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>520110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538204</t>
+          <t>539584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>56226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647145</t>
+          <t>645932</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658833</t>
+          <t>658814</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647564</t>
+          <t>647827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671570</t>
+          <t>670809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300999</t>
+          <t>1300415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327602</t>
+          <t>1327585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43709</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76847</t>
+          <t>77709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757690</t>
+          <t>758676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771655</t>
+          <t>771672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756245</t>
+          <t>756315</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>785388</t>
+          <t>784196</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1521645</t>
+          <t>1520783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554783</t>
+          <t>1551504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>91401</t>
+          <t>90999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>181182</t>
+          <t>177098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>235216</t>
+          <t>236451</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>245081</t>
+          <t>246216</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>315223</t>
+          <t>313136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3327787</t>
+          <t>3328189</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3363946</t>
+          <t>3364486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3309918</t>
+          <t>3308683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3363952</t>
+          <t>3368036</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6649099</t>
+          <t>6651186</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6719241</t>
+          <t>6718106</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27009</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281436</t>
+          <t>281654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291739</t>
+          <t>291773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>269652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283227</t>
+          <t>283035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555455</t>
+          <t>555176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572175</t>
+          <t>572835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488643</t>
+          <t>488694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499461</t>
+          <t>499684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497941</t>
+          <t>498683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514338</t>
+          <t>514198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992909</t>
+          <t>991145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1011752</t>
+          <t>1010870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305118</t>
+          <t>305295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>315217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317261</t>
+          <t>316679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626196</t>
+          <t>627184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643665</t>
+          <t>643787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357107</t>
+          <t>355755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367947</t>
+          <t>367426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361975</t>
+          <t>361474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377961</t>
+          <t>377744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724593</t>
+          <t>724065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743756</t>
+          <t>743626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196156</t>
+          <t>196634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212045</t>
+          <t>212161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407338</t>
+          <t>407726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422820</t>
+          <t>423210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28579</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250825</t>
+          <t>251601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261109</t>
+          <t>261199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251535</t>
+          <t>250954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265337</t>
+          <t>265631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507659</t>
+          <t>507754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>524899</t>
+          <t>525282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>36252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638850</t>
+          <t>639547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651750</t>
+          <t>651634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>656500</t>
+          <t>655042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>676691</t>
+          <t>676512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1299668</t>
+          <t>1300903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1325750</t>
+          <t>1324667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43729</t>
+          <t>44255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766750</t>
+          <t>765385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777764</t>
+          <t>777725</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>782438</t>
+          <t>781912</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>805349</t>
+          <t>805520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1556342</t>
+          <t>1554681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1581943</t>
+          <t>1581276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>33114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60827</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110223</t>
+          <t>111719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>158235</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154896</t>
+          <t>152690</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>209063</t>
+          <t>209726</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3333523</t>
+          <t>3334712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3360125</t>
+          <t>3361236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3386307</t>
+          <t>3385500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3434319</t>
+          <t>3432823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6729829</t>
+          <t>6729166</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6783996</t>
+          <t>6786202</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307557</t>
+          <t>307942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274725</t>
+          <t>275281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283927</t>
+          <t>283754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585633</t>
+          <t>585074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595126</t>
+          <t>595017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507638</t>
+          <t>508081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>516486</t>
+          <t>516525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497091</t>
+          <t>497084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507636</t>
+          <t>507513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009192</t>
+          <t>1009864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022249</t>
+          <t>1022746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304375</t>
+          <t>305022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312703</t>
+          <t>312938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325882</t>
+          <t>326509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338706</t>
+          <t>338300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635240</t>
+          <t>634263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649723</t>
+          <t>649384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19030</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293307</t>
+          <t>293961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307200</t>
+          <t>307481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446681</t>
+          <t>446735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465566</t>
+          <t>466206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745475</t>
+          <t>746905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>768914</t>
+          <t>768901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175011</t>
+          <t>174825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197550</t>
+          <t>196972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203990</t>
+          <t>203801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374628</t>
+          <t>374771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381752</t>
+          <t>381844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258380</t>
+          <t>258214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265867</t>
+          <t>265851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236828</t>
+          <t>237022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247263</t>
+          <t>247017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499104</t>
+          <t>497229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511606</t>
+          <t>511029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57375</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602703</t>
+          <t>602344</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615439</t>
+          <t>615602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>807702</t>
+          <t>806518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>836487</t>
+          <t>835436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1415453</t>
+          <t>1417190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1445811</t>
+          <t>1447076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69377</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102137</t>
+          <t>103694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60819</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127937</t>
+          <t>126196</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>899570</t>
+          <t>899707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>921914</t>
+          <t>921958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>612714</t>
+          <t>611157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>645474</t>
+          <t>644636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515635</t>
+          <t>1517376</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1582753</t>
+          <t>1583402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>215091</t>
+          <t>214832</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211225</t>
+          <t>212623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>278841</t>
+          <t>282968</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3378346</t>
+          <t>3379342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3411810</t>
+          <t>3412479</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3441736</t>
+          <t>3441995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3504002</t>
+          <t>3503199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6835600</t>
+          <t>6831473</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6903216</t>
+          <t>6901818</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257683</t>
+          <t>257695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269368</t>
+          <t>269260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239517</t>
+          <t>240352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254594</t>
+          <t>254354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>502832</t>
+          <t>503963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520994</t>
+          <t>521431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481740</t>
+          <t>482359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491040</t>
+          <t>491130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463787</t>
+          <t>463930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484387</t>
+          <t>483657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950296</t>
+          <t>951083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973404</t>
+          <t>972865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308241</t>
+          <t>309387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317853</t>
+          <t>317878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320938</t>
+          <t>320596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332230</t>
+          <t>331644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634612</t>
+          <t>634144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648429</t>
+          <t>648258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345027</t>
+          <t>344368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355745</t>
+          <t>355781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346909</t>
+          <t>347182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362308</t>
+          <t>362155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696715</t>
+          <t>696604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715485</t>
+          <t>715412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42914</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186103</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199226</t>
+          <t>199259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175965</t>
+          <t>176505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194187</t>
+          <t>194643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368062</t>
+          <t>368078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391153</t>
+          <t>390981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259461</t>
+          <t>259251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268827</t>
+          <t>268868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259915</t>
+          <t>260167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273061</t>
+          <t>273078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523940</t>
+          <t>524454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539352</t>
+          <t>540105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>36494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577710</t>
+          <t>578533</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598646</t>
+          <t>598932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602791</t>
+          <t>602298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622182</t>
+          <t>621998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1188063</t>
+          <t>1188240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1215393</t>
+          <t>1217378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39348</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>68565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66258</t>
+          <t>66380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102548</t>
+          <t>103897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699195</t>
+          <t>699512</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720319</t>
+          <t>721008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714331</t>
+          <t>714946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744163</t>
+          <t>745113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1423740</t>
+          <t>1422391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1460030</t>
+          <t>1459908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>114764</t>
+          <t>115374</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>147081</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>200905</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>235431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>301417</t>
+          <t>299774</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3160761</t>
+          <t>3160151</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3197225</t>
+          <t>3197002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3180742</t>
+          <t>3178292</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3232724</t>
+          <t>3232116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6353305</t>
+          <t>6354948</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6418544</t>
+          <t>6419291</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276760</t>
+          <t>276715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288213</t>
+          <t>288244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261254</t>
+          <t>259491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275165</t>
+          <t>275234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543084</t>
+          <t>544827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561627</t>
+          <t>561622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37320</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56185</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478801</t>
+          <t>479351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498093</t>
+          <t>498105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485411</t>
+          <t>484450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504674</t>
+          <t>504839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972073</t>
+          <t>970284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>999110</t>
+          <t>998399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312014</t>
+          <t>312347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321125</t>
+          <t>321115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310615</t>
+          <t>310100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329587</t>
+          <t>328212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627354</t>
+          <t>627378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647843</t>
+          <t>647891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353258</t>
+          <t>352105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367364</t>
+          <t>367386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346614</t>
+          <t>346542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366968</t>
+          <t>367055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705563</t>
+          <t>706447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732152</t>
+          <t>730237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43337</t>
+          <t>40369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196829</t>
+          <t>197783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209174</t>
+          <t>209257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187051</t>
+          <t>186807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205593</t>
+          <t>205092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>388872</t>
+          <t>391840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411283</t>
+          <t>412364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261275</t>
+          <t>261377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270958</t>
+          <t>271832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>253900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268999</t>
+          <t>269147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520110</t>
+          <t>519013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539584</t>
+          <t>538519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645932</t>
+          <t>645895</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658814</t>
+          <t>658866</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647827</t>
+          <t>646890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670809</t>
+          <t>671341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300415</t>
+          <t>1300184</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327585</t>
+          <t>1327583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>64973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>46054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77709</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758676</t>
+          <t>758474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771672</t>
+          <t>771580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756315</t>
+          <t>756547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>784196</t>
+          <t>785302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1520783</t>
+          <t>1521421</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1551504</t>
+          <t>1552438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90999</t>
+          <t>91026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>178549</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>236451</t>
+          <t>236700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>247370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>313136</t>
+          <t>309906</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3328189</t>
+          <t>3328162</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3364486</t>
+          <t>3362903</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3308683</t>
+          <t>3308434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3368036</t>
+          <t>3366585</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6651186</t>
+          <t>6654416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6718106</t>
+          <t>6716952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>20892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281654</t>
+          <t>281962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291773</t>
+          <t>291746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269652</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283035</t>
+          <t>282930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555176</t>
+          <t>555021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572835</t>
+          <t>572632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488694</t>
+          <t>489505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499684</t>
+          <t>499575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498683</t>
+          <t>497759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514198</t>
+          <t>514187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>991145</t>
+          <t>992441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010870</t>
+          <t>1011311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>27796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305295</t>
+          <t>305840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315217</t>
+          <t>315254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316679</t>
+          <t>316245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330532</t>
+          <t>330407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627184</t>
+          <t>627078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643787</t>
+          <t>643957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355755</t>
+          <t>356889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367426</t>
+          <t>367489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361474</t>
+          <t>361491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377744</t>
+          <t>377798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724065</t>
+          <t>722450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743626</t>
+          <t>742954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196634</t>
+          <t>197068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212161</t>
+          <t>212180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407726</t>
+          <t>407818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423210</t>
+          <t>423506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28484</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251601</t>
+          <t>251651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261199</t>
+          <t>261156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250954</t>
+          <t>251905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265631</t>
+          <t>265809</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507754</t>
+          <t>506691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525282</t>
+          <t>524410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36252</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46949</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639547</t>
+          <t>638616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651634</t>
+          <t>651611</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>656421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>676512</t>
+          <t>676846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300903</t>
+          <t>1302846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1324667</t>
+          <t>1324795</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44255</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765385</t>
+          <t>767042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777725</t>
+          <t>777769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>781912</t>
+          <t>781405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>805520</t>
+          <t>805088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1554681</t>
+          <t>1556259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1581276</t>
+          <t>1581318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>154872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>209726</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3334712</t>
+          <t>3334175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3361236</t>
+          <t>3361264</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3385500</t>
+          <t>3385675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3432823</t>
+          <t>3434307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6729166</t>
+          <t>6731905</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6786202</t>
+          <t>6784020</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>671</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310683</t>
+          <t>318174</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307942</t>
+          <t>315865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280117</t>
+          <t>306369</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275281</t>
+          <t>300768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283754</t>
+          <t>310066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>590799</t>
+          <t>624543</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585074</t>
+          <t>618485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595017</t>
+          <t>628361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,22 +11040,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>513841</t>
+          <t>526047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>508081</t>
+          <t>520474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>516525</t>
+          <t>528744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503347</t>
+          <t>534674</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497084</t>
+          <t>528403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507513</t>
+          <t>538716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1017189</t>
+          <t>1060720</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009864</t>
+          <t>1052501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022746</t>
+          <t>1066363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512849</t>
+          <t>544341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512849</t>
+          <t>544341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512849</t>
+          <t>544341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030242</t>
+          <t>1074000</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030242</t>
+          <t>1074000</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030242</t>
+          <t>1074000</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,22 +11383,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,17 +11418,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>23138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -11496,27 +11496,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309913</t>
+          <t>309984</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305022</t>
+          <t>304557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312938</t>
+          <t>312893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11531,17 +11531,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>333444</t>
+          <t>340397</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326509</t>
+          <t>333243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338300</t>
+          <t>345564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>643357</t>
+          <t>650382</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634263</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649384</t>
+          <t>656621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302072</t>
+          <t>362054</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293961</t>
+          <t>351391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307481</t>
+          <t>367802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>457238</t>
+          <t>401032</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446735</t>
+          <t>390339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466206</t>
+          <t>407803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>759310</t>
+          <t>763086</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>746905</t>
+          <t>749457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>768901</t>
+          <t>772839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177573</t>
+          <t>204463</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174825</t>
+          <t>201846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>201039</t>
+          <t>219313</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196972</t>
+          <t>215222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203801</t>
+          <t>222276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>378612</t>
+          <t>423775</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374771</t>
+          <t>419734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381844</t>
+          <t>427040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262719</t>
+          <t>263937</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258214</t>
+          <t>259377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265851</t>
+          <t>267121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242944</t>
+          <t>249455</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237022</t>
+          <t>243402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247017</t>
+          <t>253919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>505663</t>
+          <t>513392</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497229</t>
+          <t>506221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511029</t>
+          <t>518740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>46460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>609860</t>
+          <t>703258</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602344</t>
+          <t>694889</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615602</t>
+          <t>710300</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>820123</t>
+          <t>735320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>806518</t>
+          <t>725597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>835436</t>
+          <t>745458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1429982</t>
+          <t>1438578</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1417190</t>
+          <t>1424329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1447076</t>
+          <t>1449142</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623564</t>
+          <t>718877</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623564</t>
+          <t>718877</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623564</t>
+          <t>718877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472828</t>
+          <t>1490934</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472828</t>
+          <t>1490934</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472828</t>
+          <t>1490934</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>30867</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>88859</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70215</t>
+          <t>74800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103694</t>
+          <t>105581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>100985</t>
+          <t>110180</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60170</t>
+          <t>94382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126196</t>
+          <t>128263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>910344</t>
+          <t>776751</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>899707</t>
+          <t>767205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>921958</t>
+          <t>783733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>632242</t>
+          <t>741147</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>611157</t>
+          <t>724425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>644636</t>
+          <t>755206</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1542587</t>
+          <t>1517898</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1517376</t>
+          <t>1499815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1583402</t>
+          <t>1533696</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>78273</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>182405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>214832</t>
+          <t>226977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212623</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282968</t>
+          <t>296333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3397006</t>
+          <t>3464669</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3379342</t>
+          <t>3446974</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3412479</t>
+          <t>3477891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3470494</t>
+          <t>3527706</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3441995</t>
+          <t>3504464</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3503199</t>
+          <t>3549036</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6867499</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6831473</t>
+          <t>6965577</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6901818</t>
+          <t>7018956</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
